--- a/data_extactor/batch_10_fa/batch_0077_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0077_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | مانیتورینگ | گوش‌دادن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | زبان انگلیسی | آموزش و تربیت</t>
+          <t>مکانیک | ریاضیات | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>هماهنگی چند عضو بدن | دقت کنترل | ثبات دست و بازو | زبردستی دستی | زمان عکس‌العمل | حساسیت به مسئله | قدرت استاتیک | میزان انعطاف‌پذیری | توجه شنیداری | حساسیت شنوایی | درک عمق | استقامت | قدرت تنه | استدلال قیاسی | بیان شفاهی | انعطاف‌پذیری بستار | توجه انتخابی | دید دور | تعادل کلی بدن | وضوح گفتار | تشخیص گفتار | هماهنگی کلی بدن | دید نزدیک | زبردستی انگشتان | جهت‌گیری پاسخ | درک شفاهی | استدلال استقرایی | سرعت ادراکی | تجسم فضایی | ترتیب‌دهی اطلاعات | سرعت حرکت اعضا | کنترل نرخ | تشخیص رنگ بصری | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | مهارت دستی | زمان عکس‌العمل | حساسیت به مسئله | قدرت ایستا | انعطاف‌پذیری دامنه حرکت | توجه شنیداری | حساسیت شنوایی | درک عمق | استقامت | قدرت تنه | استدلال قیاسی | بیان شفاهی | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | تعادل کلی بدن | وضوح گفتار | تشخیص گفتار | هماهنگی کلی بدن | بینایی نزدیک | مهارت انگشتان | جهت‌گیری پاسخ | درک شفاهی | استدلال استقرایی | سرعت ادراکی | تجسم | ترتیب‌دهی اطلاعات | سرعت حرکت اعضا | کنترل نرخ | تشخیص رنگ بصری | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض آلاینده‌ها | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارگران | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض شرایط خطرناک | در معرض ارتفاعات بالا | ارتباط با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان به صورت ایستاده | نزدیکی فیزیکی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | در معرض شرایط نوری بسیار روشن یا نامناسب | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارگران | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | اهمیت دقیق یا منظم بودن | تعیین وظایف، اولویت‌ها و اهداف | در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | در معرض ارتعاش کل بدن | صرف زمان برای راه رفتن یا دویدن | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض ارتفاعات بالا | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و برج | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراک و تراکتور صنعتی | ماشین‌کارها و نصابان ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | اپراتورهای شمع‌کوب | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | پمپ‌چی‌های سر چاه</t>
+          <t>اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش‌دادن فعال | سخن‌گفتن | درک مطلب | استراتژی‌های یادگیری | نگارش</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | امور اداری و مدیریت | آموزش و تربیت | پرسنل و منابع انسانی</t>
+          <t>مکانیک | ریاضیات | مدیریت و اداره | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | حساسیت به مسئله | دید نزدیک | ثبات دست و بازو | زبردستی دستی | هماهنگی چند عضو بدن | بیان شفاهی | ترتیب‌دهی اطلاعات | درک شفاهی | زبردستی انگشتان | استدلال استقرایی | استدلال قیاسی | کنترل نرخ | توجه انتخابی | بیان کتبی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | زمان عکس‌العمل | تجسم فضایی | انعطاف‌پذیری بستار</t>
+          <t>دقت کنترل | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | بیان شفاهی | ترتیب‌دهی اطلاعات | درک شفاهی | مهارت انگشتان | استدلال استقرایی | استدلال قیاسی | کنترل نرخ | توجه انتخابی | بیان کتبی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | زمان عکس‌العمل | تجسم | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سلامت و ایمنی سایر کارگران | در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا منظم بودن | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | پیامد خطا | در معرض دماهای بسیار گرم یا سرد | اهمیت تکرار وظایف یکسان | در معرض تجهیزات خطرناک | سطح رقابت | صرف زمان به صورت ایستاده | ارتباط با دیگران | آزادی در تصمیم‌گیری | در معرض شرایط خطرناک | نزدیکی فیزیکی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | در معرض ارتعاش کل بدن | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | در معرض ارتفاعات بالا | سرعت تعیین‌شده توسط سرعت تجهیزات | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای انجام حرکات تکراری | فضای باز، زیر سقف | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | مکالمات تلفنی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | پیامد خطا | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک | سطح رقابت | صرف زمان برای ایستادن | ارتباط با دیگران | آزادی در تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | نزدیکی فیزیکی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتعاش کل بدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض ارتفاعات بالا | سرعت تعیین‌شده توسط سرعت تجهیزات | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای انجام حرکات تکراری | فضای باز، زیر سقف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین استخراج مداوم | اپراتورهای دکل، نفت و گاز | اپراتورهای لایروب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار مته‌کاری و بورینگ، فلز و پلاستیک | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری، فلز و پلاستیک | کارگران تعمیر و نگهداری، ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین فرز و صفحه تراش، فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | لوله‌کش‌ها، نصابان لوله و اتصالات | کارگران ساده، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | تیزکنندگان و سنگ‌زنان ابزار | پمپ‌چی‌های سر چاه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>اپراتورهای ماشین استخراج مداوم | اپراتورهای دکل، نفت و گاز | اپراتورهای لایروب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | پمپ‌کنندگان سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | نرم‌افزار ثبت داده‌ها | نرم‌افزار ردیابی موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و گردآوری داده‌ها SCADA | نرم‌افزار حضور و غیاب</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار ثبت داده | نرم‌افزار ردیابی موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار حضور و غیاب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش‌دادن فعال | یادگیری فعال | سخن‌گفتن | نگارش | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | خدمات مشتریان و پرسنل | مهندسی و فناوری | ایمنی و امنیت عمومی | آموزش و تربیت | زبان انگلیسی | فروش و بازاریابی | شیمی | امور اداری و مدیریت | حمل و نقل | تولید و فرآوری</t>
+          <t>مکانیک | ریاضیات | خدمات مشتری و شخصی | مهندسی و فناوری | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | فروش و بازاریابی | شیمی | مدیریت و اداره | حمل و نقل | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو بدن | دید نزدیک | حساسیت شنوایی | زمان عکس‌العمل | زبردستی دستی | توجه انتخابی | سرعت ادراکی | درک شفاهی | دید دور | توجه شنیداری | تشخیص گفتار | وضوح گفتار | بیان شفاهی | استدلال استقرایی | انعطاف‌پذیری بستار | استدلال قیاسی | قدرت استاتیک | تجسم فضایی | درک عمق | تشخیص رنگ بصری | تعادل کلی بدن | میزان انعطاف‌پذیری | قدرت تنه | کنترل نرخ | زبردستی انگشتان | اشتراک زمانی | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | حساسیت شنوایی | زمان عکس‌العمل | مهارت دستی | توجه انتخابی | سرعت ادراکی | درک شفاهی | بینایی دور | توجه شنیداری | تشخیص گفتار | وضوح گفتار | بیان شفاهی | استدلال استقرایی | انعطاف‌پذیری بستار | استدلال قیاسی | قدرت ایستا | تجسم | درک عمق | تشخیص رنگ بصری | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | کنترل نرخ | مهارت انگشتان | تقسیم توجه | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | ارتباط با دیگران | در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در معرض دماهای بسیار گرم یا سرد | در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض شرایط خطرناک | اهمیت دقیق یا منظم بودن | فشار زمانی | صرف زمان به صورت ایستاده | در وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران | در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت تکرار وظایف یکسان | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | مکالمات تلفنی | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | در معرض ارتفاعات بالا | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات | سطح رقابت | در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط خطرناک | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان برای ایستادن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات | سطح رقابت | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای سیستم و کارخانه شیمیایی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | مونتاژکنندگان موتور و سایر ماشین‌ها | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای کارخانه گاز | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | لوله‌کش‌ها، نصابان لوله و اتصالات | اپراتورهای نیروگاه | اپراتورهای پمپ، به جز پمپ‌چی‌های سر چاه | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده، نفت و گاز | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | پمپ‌چی‌های سر چاه</t>
+          <t>اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | یادگیری فعال | تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال | درک مطلب</t>
+          <t>نظارت | یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | ساخت و ساز</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو بدن | درک عمق | زمان عکس‌العمل | زبردستی دستی | ثبات دست و بازو | جهت‌گیری پاسخ | کنترل نرخ | دید دور | جهت‌گیری فضایی | دید نزدیک | توجه شنیداری | زبردستی انگشتان | دید محیطی | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تشخیص رنگ بصری | قدرت استاتیک | سرعت حرکت اعضا | اشتراک زمانی | توجه انتخابی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | درک عمق | زمان عکس‌العمل | مهارت دستی | ثبات دست و بازو | جهت‌گیری پاسخ | کنترل نرخ | بینایی دور | جهت‌گیری فضایی | بینایی نزدیک | توجه شنیداری | مهارت انگشتان | بینایی محیطی | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تشخیص رنگ بصری | قدرت ایستا | سرعت حرکت اعضا | تقسیم توجه | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | در معرض ارتعاش کل بدن | در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | در وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان به صورت نشسته | سلامت و ایمنی سایر کارگران | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | پیامد خطا | در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه روباز یا کار با تجهیزات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای نشستن | سلامت و ایمنی سایر کارکنان | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | پیامد خطا | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه روباز یا کار با تجهیزات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و برج | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراک و تراکتور صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری، ماشین‌آلات | ماشین‌کارها و نصابان ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | ریگرها | اپراتورهای مته چرخشی، نفت و گاز</t>
+          <t>اپراتورهای تجهیزات کشاورزی | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | ریگرها | اپراتورهای مته چرخشی، نفت و گاز</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم موقعیت‌یابی جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word</t>
+          <t>نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | امور اداری و مدیریت | حمل و نقل | ایمنی و امنیت عمومی | طراحی</t>
+          <t>مکانیک | مدیریت و اداره | حمل و نقل | ایمنی و امنیت عمومی | طراحی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | ثبات دست و بازو | هماهنگی چند عضو بدن | زمان عکس‌العمل | زبردستی دستی | درک عمق | دید نزدیک | کنترل نرخ | سرعت ادراکی | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم فضایی | دید دور | زبردستی انگشتان | استدلال استقرایی | تشخیص رنگ بصری | وضوح گفتار | توجه شنیداری | توجه انتخابی | انعطاف‌پذیری بستار | بیان کتبی | بیان شفاهی | درک کتبی</t>
+          <t>دقت کنترل | ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | مهارت دستی | درک عمق | بینایی نزدیک | کنترل نرخ | سرعت ادراکی | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم | بینایی دور | مهارت انگشتان | استدلال استقرایی | تشخیص رنگ بصری | وضوح گفتار | توجه شنیداری | توجه انتخابی | انعطاف‌پذیری بستار | بیان کتبی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | در معرض تجهیزات خطرناک | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | صرف زمان به صورت ایستاده | تعیین وظایف، اولویت‌ها و اهداف | در معرض ارتعاش کل بدن | ارتباط با دیگران | پیامد خطا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | در یک وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارگران | در معرض سوختگی‌های جزئی، bریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | اهمیت دقیق یا منظم بودن | در معرض دماهای بسیار گرم یا سرد | مکالمات تلفنی | در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتعاش کل بدن | ارتباط با دیگران | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | در یک وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | مکالمات تلفنی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورهای دکل، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار مته‌کاری و بورینگ، فلز و پلاستیک | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری، ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین فرز و صفحه تراش، فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | تیزکنندگان و سنگ‌زنان ابزار | پمپ‌چی‌های سر چاه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورهای دکل، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | پمپ‌کنندگان سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Blaster's Tool and Supply Company Blaster's Calculator | Datavis DBS Designer | DetNet ViewShot | نرم‌افزار ESRI ArcGIS | نرم‌افزار سیستم موقعیت‌یابی جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+          <t>Autodesk AutoCAD | Blaster's Tool and Supply Company Blaster's Calculator | Datavis DBS Designer | DetNet ViewShot | نرم‌افزار ESRI ArcGIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | مانیتورینگ | تفکر انتقادی | سخن‌گفتن | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | قانون و حکومت | ریاضیات | مهندسی و فناوری | حمل و نقل | خدمات مشتریان و پرسنل | امور اداری و مدیریت | زبان انگلیسی | تولید و فرآوری | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | ریاضیات | مهندسی و فناوری | حمل و نقل | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | تولید و فرآوری | مکانیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | زبردستی دستی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | بیان شفاهی | زبردستی انگشتان | هماهنگی چند عضو بدن | زمان عکس‌العمل | تشخیص رنگ بصری | دقت کنترل | توجه انتخابی | درک عمق | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم فضایی | تشخیص گفتار | دید دور | حساسیت شنوایی | میزان انعطاف‌پذیری | قدرت تنه | قدرت استاتیک | اشتراک زمانی | درک کتبی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | مهارت دستی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | بیان شفاهی | مهارت انگشتان | هماهنگی چند عضو | زمان عکس‌العمل | تشخیص رنگ بصری | دقت کنترل | توجه انتخابی | درک عمق | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | تشخیص گفتار | بینایی دور | حساسیت شنوایی | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | تقسیم توجه | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض شرایط خطرناک | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | در معرض آلاینده‌ها | ارتباط با دیگران | فشار زمانی | پیامدهای کاری و نتایج سایر کارگران | کار با یا مشارکت در یک گروه یا تیم کاری | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | در معرض دماهای بسیار گرم یا سرد | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامد خطا | در معرض تجهیزات خطرناک | در وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | در یک وسیله نقلیه روباز یا کار با تجهیزات | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | در یک وسیله نقلیه روباز یا کار با تجهیزات | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، ریگینگ و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات آهنگری، فلز و پلاستیک | کارگران حذف مواد خطرناک | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری، ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای شمع‌کوب | اپراتورهای پمپ، به جز پمپ‌چی‌های سر چاه | ریگرها | پیچ‌کنندگان سقف، معدن | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جوشکاری، لحیم‌کاری نرم و سخت</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران حذف مواد خطرناک | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | ریگرها | پیچ‌کنندگان سقف، معدن | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | قانون و حکومت | آموزش و تربیت</t>
+          <t>مکانیک | تولید و فرآوری | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | هماهنگی چند عضو بدن | زمان عکس‌العمل | دید نزدیک | کنترل نرخ | حساسیت شنوایی | درک عمق | توجه انتخابی | دید دور | زبردستی دستی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | میزان انعطاف‌پذیری | قدرت تنه | جهت‌گیری پاسخ | توجه شنیداری | تشخیص رنگ بصری | قدرت استاتیک | زبردستی انگشتان | اشتراک زمانی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
+          <t>دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | کنترل نرخ | حساسیت شنوایی | درک عمق | توجه انتخابی | بینایی دور | مهارت دستی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | انعطاف‌پذیری دامنه حرکت | قدرت تنه | جهت‌گیری پاسخ | توجه شنیداری | تشخیص رنگ بصری | قدرت ایستا | مهارت انگشتان | تقسیم توجه | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | پیامد خطا | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا منظم بودن | آزادی در تصمیم‌گیری | در معرض شرایط نوری بسیار روشن یا نامناسب | در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان به صورت ایستاده | سرعت تعیین‌شده توسط سرعت تجهیزات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | در معرض ارتعاش کل بدن | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | پیامد خطا | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای ایستادن | سرعت تعیین‌شده توسط سرعت تجهیزات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | اپراتورهای جرثقیل و برج | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراک و تراکتور صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری، ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین فرز و صفحه تراش، فلز و پلاستیک | ماشین‌کارها و نصابان ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | پیچ‌کنندگان سقف، معدن | اپراتورهای مته چرخشی، نفت و گاز</t>
+          <t>اپراتورهای تجهیزات کشاورزی | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | پیچ‌کنندگان سقف، معدن | اپراتورهای مته چرخشی، نفت و گاز</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش‌دادن فعال | سخن‌گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | آموزش و تربیت | مکانیک | ایمنی و امنیت عمومی</t>
+          <t>تولید و فرآوری | آموزش و پرورش | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دقت کنترل | ثبات دست و بازو | میزان انعطاف‌پذیری | زبردستی دستی | حساسیت به مسئله | هماهنگی چند عضو بدن | زمان عکس‌العمل | دید نزدیک | درک عمق | ترتیب‌دهی اطلاعات | قدرت استاتیک | توجه انتخابی | جهت‌گیری پاسخ | کنترل نرخ | قدرت تنه | دید دور | تعادل کلی بدن | استقامت | تشخیص گفتار | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | زبردستی انگشتان | اشتراک زمانی | تجسم فضایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | مهارت دستی | حساسیت به مسئله | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | درک عمق | ترتیب‌دهی اطلاعات | قدرت ایستا | توجه انتخابی | جهت‌گیری پاسخ | کنترل نرخ | قدرت تنه | بینایی دور | تعادل کلی بدن | استقامت | تشخیص گفتار | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | مهارت انگشتان | تقسیم توجه | تجسم | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض تجهیزات خطرناک | در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارگران | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فشار زمانی | در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه یا تیم کاری | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای خم کردن یا چرخاندن بدن | در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | ارتباط با دیگران | داخل ساختمان، بدون کنترل شرایط محیطی | صرف زمان برای راه رفتن یا دویدن | در معرض ارتعاش کل بدن | نزدیکی فیزیکی | اهمیت دقیق یا منظم بودن | پیامد خطا | پیامدهای کاری و نتایج سایر کارگران | اهمیت تکرار وظایف یکسان | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | فراوانی تصمیم‌گیری | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | ارتباط با دیگران | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض ارتعاش کل بدن | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، ریگینگ و سیستم‌های هواپیما | نجاران | اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و برج | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات آهنگری، فلز و پلاستیک | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | کارگران آهن آرماتوربند و میلگردکار | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | ورق‌کاران | کارگران آهن و فولاد ساختمانی | سازندگان و جفت‌کنندگان فلزات ساختمانی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نجّاران | اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و تاور | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | کارگران آهن تقویتی و میلگرد | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | آموزش و تربیت</t>
+          <t>مکانیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دقت کنترل | زمان عکس‌العمل | هماهنگی چند عضو بدن | حساسیت به مسئله | ثبات دست و بازو | زبردستی دستی | کنترل نرخ | دید نزدیک | توجه انتخابی | سرعت ادراکی | درک عمق | قدرت تنه | اشتراک زمانی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | دید دور | میزان انعطاف‌پذیری | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | زمان عکس‌العمل | هماهنگی چند عضو | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | کنترل نرخ | بینایی نزدیک | توجه انتخابی | سرعت ادراکی | درک عمق | قدرت تنه | تقسیم توجه | وضوح گفتار | تشخیص گفتار | توجه شنیداری | بینایی دور | انعطاف‌پذیری دامنه حرکت | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>در معرض آلاینده‌ها | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | در معرض تجهیزات خطرناک | در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض ارتعاش کل بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارگران | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در معرض شرایط نوری بسیار روشن یا نامناسب | صرف زمان برای انجام حرکات تکراری | در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای خم کردن یا چرخاندن بدن | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض ارتعاش کل بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای خم کردن یا چرخاندن بدن | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و برج | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | رانندگان کامیون‌های سنگین و تریلی | کمک‌کارگران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراک و تراکتور صنعتی | کارگران دستی و جابجاکنندگان بار، کالا و مواد | اپراتورهای تجهیزات قطع درختان و جنگل‌داری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری، ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای شمع‌کوب | تعمیرکاران واگن‌های راه‌آهن | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | ریگرها | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها</t>
+          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | رانندگان کامیون‌های سنگین و تریلی | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای تجهیزات چوب‌بری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | تعمیرکنندگان واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | ریگرها | بارگیران واگن مخزنی، کامیون و کشتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | نرم‌افزار کنترل نظارتی و گردآوری داده‌ها SCADA</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش‌دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چند عضو بدن | دقت کنترل | قدرت استاتیک | قدرت تنه | استقامت | دید نزدیک | دید دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | میزان انعطاف‌پذیری | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | در معرض تجهیزات خطرناک | در معرض شرایط خطرناک | در معرض آلاینده‌ها | در معرض ارتعاش کل بدن | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | داخل ساختمان، بدون کنترل شرایط محیطی | در وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض شرایط نوری بسیار روشن یا نامناسب | سلامت و ایمنی سایر کارگران | پیامد خطا | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | اهمیت دقیق یا منظم بودن | در معرض دماهای بسیار گرم یا سرد</t>
+          <t>قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | محیط داخلی، بدون کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | سلامت و ایمنی سایر کارکنان | پیامد خطا | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین استخراج مداوم | پیچ‌کنندگان سقف، معدن | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | حفاران زمین، به جز نفت و گاز | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | شکاف‌دهندگان سنگ، معدن سنگ | کمک‌کارگران--کارگران استخراج | کارگران استخراج، سایر | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان نوار نقاله | اپراتورهای بالابر و وینچ | تکنسین‌های بهداشت و ایمنی حرفه‌ای | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | کارگران ساختمانی | رانندگان کامیون‌های سنگین و تریلی</t>
+          <t>اپراتورهای ماشین استخراج مداوم | پیچ‌کنندگان سقف، معدن | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | حفاران زمین، به جز نفت و گاز | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | سنگ‌شکنان معدن | دستیاران--کارگران استخراج | کارگران استخراج، سایر | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان نوار نقاله | اپراتورهای بالابر و وینچ | تکنسین‌های بهداشت و ایمنی شغلی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | کارگران ساختمانی | رانندگان کامیون‌های سنگین و تریلی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0077_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0077_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | زبان انگلیسی | آموزش و تدریس</t>
+          <t>مکانیک | ریاضیات | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>هماهنگی میان اندام‌ها | دقت در کنترل | ثبات دست و بازو | چابکی دستی | زمان واکنش | حساسیت به مسئله | قدرت ایستا | انعطاف‌پذیری بالاتنه | توجه شنیداری | حساسیت شنوایی | ادراک عمق | پایداری و توان جسمانی | قدرت عضلات تنه | استدلال قیاسی | بیان شفاهی | کشف الگو | توجه انتخابی | دید دور | تعادل بدنی | وضوح گفتار | تشخیص گفتار | هماهنگی کلی بدن | دید نزدیک | چابکی انگشتان | گرایش پاسخ‌دهی | درک شفاهی | استدلال استقرایی | سرعت ادراک | تجسم فضایی | مرتب‌سازی اطلاعات | سرعت حرکت اندام‌ها | کنترل نرخ حرکت | تشخیص رنگ‌ها | سرعت در شناسایی | طبقه‌بندی مفاهیم</t>
+          <t>هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | مهارت دستی | زمان عکس‌العمل | حساسیت به مسئله | قدرت ایستا | انعطاف‌پذیری دامنه حرکت | توجه شنیداری | حساسیت شنوایی | درک عمق | استقامت | قدرت تنه | استدلال قیاسی | بیان شفاهی | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | تعادل کلی بدن | وضوح گفتار | تشخیص گفتار | هماهنگی کلی بدن | بینایی نزدیک | مهارت انگشتان | جهت‌گیری پاسخ | درک شفاهی | استدلال استقرایی | سرعت ادراکی | تجسم | ترتیب‌دهی اطلاعات | سرعت حرکت اعضا | کنترل نرخ | تشخیص رنگ بصری | سرعت بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و بالابر برجی | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | تکنسین‌های نصب و تعمیر خطوط انتقال برق | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | اپراتورهای کشنده و لیفتراک‌های صنعتی | ماشین‌کاران و مونتاژکاران صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای ماشین‌آلات آسفالت‌کاری و تراکم خاک | اپراتورهای شمع‌کوب | ریگرها و متصدیان مهار بار | اپراتورهای حفاری دورانی نفت و گاز | کارگران همه‌کاره دکل‌های نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | پمپ‌چی‌های سرچاهی</t>
+          <t>اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نگارش</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | مدیریت و امور اداری | آموزش و تدریس | پرسنلی و منابع انسانی</t>
+          <t>مکانیک | ریاضیات | مدیریت و اداره | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت در کنترل | حساسیت به مسئله | دید نزدیک | ثبات دست و بازو | چابکی دستی | هماهنگی میان اندام‌ها | بیان شفاهی | مرتب‌سازی اطلاعات | درک شفاهی | چابکی انگشتان | استدلال استقرایی | استدلال قیاسی | کنترل نرخ حرکت | توجه انتخابی | بیان کتبی | سرعت ادراک | طبقه‌بندی مفاهیم | درک کتبی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | زمان واکنش | تجسم فضایی | کشف الگو</t>
+          <t>دقت کنترل | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | بیان شفاهی | ترتیب‌دهی اطلاعات | درک شفاهی | مهارت انگشتان | استدلال استقرایی | استدلال قیاسی | کنترل نرخ | توجه انتخابی | بیان کتبی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | زمان عکس‌العمل | تجسم | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های استخراج پیوسته | دکل‌بانان نفت و گاز | اپراتورهای لایروب | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای حفاری فلز و پلاستیک | حفاران زمین، به‌جز نفت و گاز | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | تنظیم‌کنندگان و اپراتورهای دستگاه‌های تراش فلز و پلاستیک | تعمیرکاران و نگه‌دارندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای دستگاه‌های فرز فلز و پلاستیک | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای سیستم‌های پمپاژ نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | لوله‌کش‌ها و تکنسین‌های خطوط لوله | کارگران همه‌کاره دکل‌های نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | سنگ‌زن‌ها و ابزارتیزکن‌ها | پمپ‌چی‌های سرچاهی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>اپراتورهای ماشین‌های استخراج پیوسته | دکل‌بانان نفت و گاز | اپراتورهای لایروب | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | اپراتورهای پمپ سرچاهی نفت و گاز | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | یادگیری فعال | سخن گفتن | نگارش | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | ایمنی و امنیت عمومی | آموزش و تدریس | زبان انگلیسی | بازاریابی و فروش | شیمی | مدیریت و امور اداری | ترابری | تولید و فراوری</t>
+          <t>مکانیک | ریاضیات | خدمات مشتری و شخصی | مهندسی و فناوری | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | فروش و بازاریابی | شیمی | مدیریت و اداره | حمل و نقل | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | دقت در کنترل | هماهنگی میان اندام‌ها | دید نزدیک | حساسیت شنوایی | زمان واکنش | چابکی دستی | توجه انتخابی | سرعت ادراک | درک شفاهی | دید دور | توجه شنیداری | تشخیص گفتار | وضوح گفتار | بیان شفاهی | استدلال استقرایی | کشف الگو | استدلال قیاسی | قدرت ایستا | تجسم فضایی | ادراک عمق | تشخیص رنگ‌ها | تعادل بدنی | انعطاف‌پذیری بالاتنه | قدرت عضلات تنه | کنترل نرخ حرکت | چابکی انگشتان | تقسیم توجه | درک کتبی | طبقه‌بندی مفاهیم | مرتب‌سازی اطلاعات | بیان کتبی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | حساسیت شنوایی | زمان عکس‌العمل | مهارت دستی | توجه انتخابی | سرعت ادراکی | درک شفاهی | بینایی دور | توجه شنیداری | تشخیص گفتار | وضوح گفتار | بیان شفاهی | استدلال استقرایی | انعطاف‌پذیری بستار | استدلال قیاسی | قدرت ایستا | تجسم | درک عمق | تشخیص رنگ بصری | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | کنترل نرخ | مهارت انگشتان | تقسیم توجه | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای کارخانه‌ها و سیستم‌های شیمیایی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | مونتاژکاران موتور و تجهیزات صنعتی | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | اپراتورهای کمپرسور گاز و ایستگاه‌های تقویت فشار | اپراتورهای پالایشگاه گاز | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | تعمیرکاران ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای سیستم‌های پمپاژ نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | لوله‌کش‌ها و تکنسین‌های خطوط لوله | اپراتورهای نیروگاه برق | پمپ‌چی‌ها، به‌جز پمپ‌چی‌های سرچاهی | اپراتورهای حفاری دورانی نفت و گاز | کارگران همه‌کاره دکل‌های نفت و گاز | سرویس‌کاران سپتیک‌تانک و لایروب‌های شبکه فاضلاب | پمپ‌چی‌های سرچاهی</t>
+          <t>اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | یادگیری فعال | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | ساخت و ساز ساختمان</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دقت در کنترل | هماهنگی میان اندام‌ها | ادراک عمق | زمان واکنش | چابکی دستی | ثبات دست و بازو | گرایش پاسخ‌دهی | کنترل نرخ حرکت | دید دور | جهت‌یابی فضایی | دید نزدیک | توجه شنیداری | چابکی انگشتان | دید پیرامونی | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تشخیص رنگ‌ها | قدرت ایستا | سرعت حرکت اندام‌ها | تقسیم توجه | توجه انتخابی | تجسم فضایی | سرعت ادراک | کشف الگو | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | درک عمق | زمان عکس‌العمل | مهارت دستی | ثبات دست و بازو | جهت‌گیری پاسخ | کنترل نرخ | بینایی دور | جهت‌گیری فضایی | بینایی نزدیک | توجه شنیداری | مهارت انگشتان | بینایی محیطی | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تشخیص رنگ بصری | قدرت ایستا | سرعت حرکت اعضا | تقسیم توجه | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات کشاورزی | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و بالابر برجی | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | تعمیرکاران ماشین‌آلات صنعتی | اپراتورهای کشنده و لیفتراک‌های صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | تعمیرکاران و نگه‌دارندگان ماشین‌آلات | ماشین‌کاران و مونتاژکاران صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای ماشین‌آلات آسفالت‌کاری و تراکم خاک | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | ریگرها و متصدیان مهار بار | اپراتورهای حفاری دورانی نفت و گاز</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزارهای سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | Microsoft Office | Microsoft Word</t>
+          <t>نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | مدیریت و امور اداری | ترابری | ایمنی و امنیت عمومی | طراحی</t>
+          <t>مکانیک | مدیریت و اداره | حمل و نقل | ایمنی و امنیت عمومی | طراحی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت در کنترل | ثبات دست و بازو | هماهنگی میان اندام‌ها | زمان واکنش | چابکی دستی | ادراک عمق | دید نزدیک | کنترل نرخ حرکت | سرعت ادراک | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | تجسم فضایی | دید دور | چابکی انگشتان | استدلال استقرایی | تشخیص رنگ‌ها | وضوح گفتار | توجه شنیداری | توجه انتخابی | کشف الگو | بیان کتبی | بیان شفاهی | درک کتبی</t>
+          <t>دقت کنترل | ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | مهارت دستی | درک عمق | بینایی نزدیک | کنترل نرخ | سرعت ادراکی | حساسیت شنوایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم | بینایی دور | مهارت انگشتان | استدلال استقرایی | تشخیص رنگ بصری | وضوح گفتار | توجه شنیداری | توجه انتخابی | انعطاف‌پذیری بستار | بیان کتبی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | دکل‌بانان نفت و گاز | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای حفاری فلز و پلاستیک | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | تعمیرکاران و نگه‌دارندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای دستگاه‌های فرز فلز و پلاستیک | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای ماشین‌آلات آسفالت‌کاری و تراکم خاک | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | اپراتورهای حفاری دورانی نفت و گاز | کارگران همه‌کاره دکل‌های نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | سنگ‌زن‌ها و ابزارتیزکن‌ها | پمپ‌چی‌های سرچاهی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | دکل‌بانان نفت و گاز | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | اپراتورهای پمپ سرچاهی نفت و گاز | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | ریاضیات | مهندسی و فناوری | ترابری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | تولید و فراوری | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | ریاضیات | مهندسی و فناوری | حمل و نقل | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | تولید و فرآوری | مکانیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | چابکی دستی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | ثبات دست و بازو | بیان شفاهی | چابکی انگشتان | هماهنگی میان اندام‌ها | زمان واکنش | تشخیص رنگ‌ها | دقت در کنترل | توجه انتخابی | ادراک عمق | وضوح گفتار | طبقه‌بندی مفاهیم | کشف الگو | سرعت ادراک | تجسم فضایی | تشخیص گفتار | دید دور | حساسیت شنوایی | انعطاف‌پذیری بالاتنه | قدرت عضلات تنه | قدرت ایستا | تقسیم توجه | درک کتبی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | مهارت دستی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | بیان شفاهی | مهارت انگشتان | هماهنگی چند عضو | زمان عکس‌العمل | تشخیص رنگ بصری | دقت کنترل | توجه انتخابی | درک عمق | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | تشخیص گفتار | بینایی دور | حساسیت شنوایی | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | تقسیم توجه | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات آهنگری فلز و پلاستیک | کارگران پاک‌سازی و امحای پسماندهای خطرناک | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | تعمیرکاران و نگه‌دارندگان ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای شمع‌کوب | پمپ‌چی‌ها، به‌جز پمپ‌چی‌های سرچاهی | ریگرها و متصدیان مهار بار | راک‌بولت‌کاران معدن | اپراتورهای حفاری دورانی نفت و گاز | کارگران همه‌کاره دکل‌های نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | تنظیم‌کنندگان و اپراتورهای دستگاه‌های جوشکاری، لحیم‌کاری و بریزینگ</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | راک‌بولت‌کاران معدن | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | حقوق و مقررات دولتی | آموزش و تدریس</t>
+          <t>مکانیک | تولید و فرآوری | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دقت در کنترل | ثبات دست و بازو | حساسیت به مسئله | هماهنگی میان اندام‌ها | زمان واکنش | دید نزدیک | کنترل نرخ حرکت | حساسیت شنوایی | ادراک عمق | توجه انتخابی | دید دور | چابکی دستی | سرعت ادراک | کشف الگو | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | انعطاف‌پذیری بالاتنه | قدرت عضلات تنه | گرایش پاسخ‌دهی | توجه شنیداری | تشخیص رنگ‌ها | قدرت ایستا | چابکی انگشتان | تقسیم توجه | تجسم فضایی | طبقه‌بندی مفاهیم | مرتب‌سازی اطلاعات</t>
+          <t>دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | کنترل نرخ | حساسیت شنوایی | درک عمق | توجه انتخابی | بینایی دور | مهارت دستی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | انعطاف‌پذیری دامنه حرکت | قدرت تنه | جهت‌گیری پاسخ | توجه شنیداری | تشخیص رنگ بصری | قدرت ایستا | مهارت انگشتان | تقسیم توجه | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات کشاورزی | اپراتورهای جرثقیل و بالابر برجی | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | تعمیرکاران ماشین‌آلات صنعتی | اپراتورهای کشنده و لیفتراک‌های صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | تعمیرکاران و نگه‌دارندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای دستگاه‌های فرز فلز و پلاستیک | ماشین‌کاران و مونتاژکاران صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای ماشین‌آلات آسفالت‌کاری و تراکم خاک | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | راک‌بولت‌کاران معدن | اپراتورهای حفاری دورانی نفت و گاز</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | راک‌بولت‌کاران معدن | حفاران دورانی نفت و گاز</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | آموزش و تدریس | مکانیک | ایمنی و امنیت عمومی</t>
+          <t>تولید و فرآوری | آموزش و پرورش | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دقت در کنترل | ثبات دست و بازو | انعطاف‌پذیری بالاتنه | چابکی دستی | حساسیت به مسئله | هماهنگی میان اندام‌ها | زمان واکنش | دید نزدیک | ادراک عمق | مرتب‌سازی اطلاعات | قدرت ایستا | توجه انتخابی | گرایش پاسخ‌دهی | کنترل نرخ حرکت | قدرت عضلات تنه | دید دور | تعادل بدنی | پایداری و توان جسمانی | تشخیص گفتار | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | چابکی انگشتان | تقسیم توجه | تجسم فضایی | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | مهارت دستی | حساسیت به مسئله | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | درک عمق | ترتیب‌دهی اطلاعات | قدرت ایستا | توجه انتخابی | جهت‌گیری پاسخ | کنترل نرخ | قدرت تنه | بینایی دور | تعادل کلی بدن | استقامت | تشخیص گفتار | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | مهارت انگشتان | تقسیم توجه | تجسم | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح و سیستم‌های هواپیما | نجاران | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و بالابر برجی | حفاران زمین، به‌جز نفت و گاز | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات آهنگری فلز و پلاستیک | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای شمع‌کوب | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | آرماتوربندها | ریگرها و متصدیان مهار بار | اپراتورهای حفاری دورانی نفت و گاز | ورق‌کاران فلزی | اسکلت‌سازان فلزی | مونتاژکاران و نصابان قطعات سازه‌های فلزی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نجاران و درودگران | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و تاورکرین | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارشناسان مواد منفجره و آتش‌باری | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | آرماتوربندان و نصابان میلگرد | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | آموزش و تدریس</t>
+          <t>مکانیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دقت در کنترل | زمان واکنش | هماهنگی میان اندام‌ها | حساسیت به مسئله | ثبات دست و بازو | چابکی دستی | کنترل نرخ حرکت | دید نزدیک | توجه انتخابی | سرعت ادراک | ادراک عمق | قدرت عضلات تنه | تقسیم توجه | وضوح گفتار | تشخیص گفتار | توجه شنیداری | دید دور | انعطاف‌پذیری بالاتنه | تجسم فضایی | طبقه‌بندی مفاهیم | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | زمان عکس‌العمل | هماهنگی چند عضو | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | کنترل نرخ | بینایی نزدیک | توجه انتخابی | سرعت ادراکی | درک عمق | قدرت تنه | تقسیم توجه | وضوح گفتار | تشخیص گفتار | توجه شنیداری | بینایی دور | انعطاف‌پذیری دامنه حرکت | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس، کامیون و موتورهای دیزلی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای نوار نقاله | اپراتورهای جرثقیل و بالابر برجی | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | رانندگان کامیون‌های سنگین و تریلر | کارگران کمکی استخراج | اپراتورهای بالابر و وینچ | اپراتورهای کشنده و لیفتراک‌های صنعتی | کارگران جابه‌جایی دستی بار و اثاثیه | اپراتورهای ماشین‌آلات الوارسازی | تغذیه‌کنندگان و متصدیان خروجی ماشین‌آلات | تعمیرکاران و نگه‌دارندگان ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | اپراتورهای شمع‌کوب | تعمیرکاران واگن‌های راه‌آهن | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | ریگرها و متصدیان مهار بار | متصدیان بارگیری مخازن ریلی، جاده‌ای و کشتی</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | رانندگان خودروهای سنگین و کشنده‌ها | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | تعمیرکار واگن قطار | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | تولید و فراوری | فیزیک</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | تولید و فرآوری | فیزیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی میان اندام‌ها | دقت در کنترل | قدرت ایستا | قدرت عضلات تنه | پایداری و توان جسمانی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل بدنی | انعطاف‌پذیری بالاتنه | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های استخراج پیوسته | راک‌بولت‌کاران معدن | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | اپراتورهای بیل مکانیکی، لودر و درگ‌لاین در معادن روباز | حفاران زمین، به‌جز نفت و گاز | کارشناسان مواد منفجره و آتش‌باری | سنگ‌شکن‌ها و قواره‌سازان سنگ معدن در معدن سنگ | کارگران کمکی استخراج | سایر کارگران استخراج | مهندسان معدن و زمین‌شناسی، از جمله مهندسان ایمنی معدن | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | اپراتورهای ماشین‌آلات عمرانی و ساختمانی | مکانیک‌های تجهیزات سنگین متحرک، به‌جز موتور | تعمیرکاران ماشین‌آلات صنعتی | اپراتورهای نوار نقاله | اپراتورهای بالابر و وینچ | تکنسین‌های ایمنی و بهداشت حرفه‌ای | تکنسین‌های زمین‌شناسی، به‌جز هیدرولوژی | کارگران ساختمانی | رانندگان کامیون‌های سنگین و تریلر</t>
+          <t>اپراتورهای ماشین‌های استخراج پیوسته | راک‌بولت‌کاران معدن | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | حفاران زمین، به‌جز نفت و گاز | کارشناسان مواد منفجره و آتش‌باری | سنگ‌شکنان و برش‌کاران سنگ معدن | کارگران کمکی استخراج معدن | سایر کارگران استخراج معدن و نفت | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | مکانیک تجهیزات سنگین متحرک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان نوار نقاله | اپراتورهای بالابر و وینچ | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | کارگران ساختمانی | رانندگان خودروهای سنگین و کشنده‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
